--- a/api/templates/mtb_detected_rr_detected/uk.xlsx
+++ b/api/templates/mtb_detected_rr_detected/uk.xlsx
@@ -1,33 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\mtb_detected_rr_detected\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31BC72A-51AE-41E4-AEA5-32DB27F8AE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="20980" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Виявлено MTB, виявлено RR" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>&lt;UserFullName&gt;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>Виявлено MTB, виявлено RR</t>
+  </si>
+  <si>
+    <t>Дати: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Райони: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -36,12 +37,42 @@
     <t>#</t>
   </si>
   <si>
+    <t>Ідентифікатор пацієнта</t>
+  </si>
+  <si>
+    <t>Ідентифікатор пацієнта 2</t>
+  </si>
+  <si>
+    <t>Ідентифікатор справи</t>
+  </si>
+  <si>
+    <t>ID зразка</t>
+  </si>
+  <si>
+    <t>Вік</t>
+  </si>
+  <si>
+    <t>Пристрій</t>
+  </si>
+  <si>
+    <t>Дата тестування</t>
+  </si>
+  <si>
     <t>MTB</t>
   </si>
   <si>
     <t>RIF</t>
   </si>
   <si>
+    <t>Текст результатів</t>
+  </si>
+  <si>
+    <t>Код помилки</t>
+  </si>
+  <si>
+    <t>Тестові примітки</t>
+  </si>
+  <si>
     <t>&lt;#&gt;</t>
   </si>
   <si>
@@ -79,73 +110,24 @@
   </si>
   <si>
     <t>&lt;notes&gt;</t>
-  </si>
-  <si>
-    <t>Виявлено MTB, виявлено RR</t>
-  </si>
-  <si>
-    <t>Дати: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Райони: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>Сайти: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>Ідентифікатор пацієнта</t>
-  </si>
-  <si>
-    <t>Ідентифікатор пацієнта 2</t>
-  </si>
-  <si>
-    <t>Ідентифікатор справи</t>
-  </si>
-  <si>
-    <t>ID зразка</t>
-  </si>
-  <si>
-    <t>Вік</t>
-  </si>
-  <si>
-    <t>Пристрій</t>
-  </si>
-  <si>
-    <t>Дата тестування</t>
-  </si>
-  <si>
-    <t>Текст результатів</t>
-  </si>
-  <si>
-    <t>Код помилки</t>
-  </si>
-  <si>
-    <t>Тестові примітки</t>
-  </si>
-  <si>
-    <t>Області: &lt;States&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -153,7 +135,24 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
@@ -161,25 +160,161 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -192,8 +327,194 @@
         <bgColor rgb="FF00CCFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -231,102 +552,391 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="60% - Accent6" xfId="2" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="3" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="4" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="5" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="6" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="7" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="9" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="10" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="11" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="14" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="15" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="16" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="17" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="18" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="19" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="20" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="21" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="22" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="23" builtinId="32"/>
+    <cellStyle name="Bad" xfId="24" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="25" builtinId="42"/>
+    <cellStyle name="Total" xfId="26" builtinId="25"/>
+    <cellStyle name="Output" xfId="27" builtinId="21"/>
+    <cellStyle name="Currency" xfId="28" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="29" builtinId="38"/>
+    <cellStyle name="Note" xfId="30" builtinId="10"/>
+    <cellStyle name="Input" xfId="31" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="32" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="33" builtinId="22"/>
+    <cellStyle name="Good" xfId="34" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="35" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="36" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="37" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="38" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
+    <cellStyle name="Title" xfId="40" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="41" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="42" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="43" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="44" builtinId="17"/>
+    <cellStyle name="Comma" xfId="45" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="46" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="47" builtinId="40"/>
+    <cellStyle name="Percent" xfId="48" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="49" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="003CC0DD"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
       <rgbColor rgb="00003366"/>
       <rgbColor rgb="00339966"/>
       <rgbColor rgb="00003300"/>
@@ -340,9 +950,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -391,7 +998,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -424,26 +1031,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -476,23 +1066,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -634,40 +1207,35 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.78125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="7.4453125" customWidth="1"/>
     <col min="2" max="4" width="24.21875" customWidth="1"/>
     <col min="5" max="5" width="23.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.890625" style="1" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="18.44140625" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" customWidth="1"/>
-    <col min="10" max="12" width="16.77734375" customWidth="1"/>
-    <col min="13" max="13" width="60.77734375" customWidth="1"/>
+    <col min="8" max="8" width="18.4453125" customWidth="1"/>
+    <col min="9" max="9" width="14.4453125" customWidth="1"/>
+    <col min="10" max="12" width="16.78125" customWidth="1"/>
+    <col min="13" max="13" width="60.78125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="20" spans="1:13">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
+      <c r="F1" s="10"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -676,208 +1244,207 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="14.8" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" ht="14.8" spans="1:13">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" ht="14.8" spans="1:13">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" ht="14.8" spans="1:13">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" ht="14.8" spans="1:13">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" ht="14.8" spans="2:13">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" ht="15.55" spans="1:13">
+      <c r="A8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="11"/>
+    </row>
+    <row r="9" ht="30.9" customHeight="1" spans="1:13">
+      <c r="A9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" ht="14.8" spans="1:13">
+      <c r="A10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-    </row>
-    <row r="8" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" spans="1:13" ht="30.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="H10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="J10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="9" t="s">
+      <c r="K10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/api/templates/mtb_detected_rr_detected/uk.xlsx
+++ b/api/templates/mtb_detected_rr_detected/uk.xlsx
@@ -1,33 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Виявлено MTB, виявлено RR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="Виявлено MTB, виявлено RR" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t xml:space="preserve">Виявлено MTB, виявлено RR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дати: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Області: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Райони: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сайти: &lt;Sites&gt;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>Виявлено MTB, виявлено RR</t>
+  </si>
+  <si>
+    <t>Дати: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Райони: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -36,16 +37,16 @@
     <t>#</t>
   </si>
   <si>
-    <t xml:space="preserve">Ідентифікатор пацієнта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ідентифікатор пацієнта 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ідентифікатор справи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID зразка</t>
+    <t>Ідентифікатор пацієнта</t>
+  </si>
+  <si>
+    <t>Ідентифікатор пацієнта 2</t>
+  </si>
+  <si>
+    <t>Ідентифікатор справи</t>
+  </si>
+  <si>
+    <t>ID зразка</t>
   </si>
   <si>
     <t>Вік</t>
@@ -54,13 +55,16 @@
     <t>Пристрій</t>
   </si>
   <si>
-    <t xml:space="preserve">ідентифікатор інструменту</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дата тестування</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ім'я аналізу</t>
+    <t>Сайт</t>
+  </si>
+  <si>
+    <t>ідентифікатор інструменту</t>
+  </si>
+  <si>
+    <t>Дата тестування</t>
+  </si>
+  <si>
+    <t>Ім'я аналізу</t>
   </si>
   <si>
     <t>MTB</t>
@@ -69,13 +73,13 @@
     <t>RIF</t>
   </si>
   <si>
-    <t xml:space="preserve">Текст результатів</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Код помилки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестові примітки</t>
+    <t>Текст результатів</t>
+  </si>
+  <si>
+    <t>Код помилки</t>
+  </si>
+  <si>
+    <t>Тестові примітки</t>
   </si>
   <si>
     <t>&lt;#&gt;</t>
@@ -97,6 +101,9 @@
   </si>
   <si>
     <t>&lt;deviceName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;instrumentSerial&gt;</t>
@@ -126,161 +133,39 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="dd\-mm\-yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.000000"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.000000"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.000000"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.000000"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.000000"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15.000000"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18.000000"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color indexed="2"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.000000"/>
-      <color indexed="20"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.000000"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.000000"/>
-      <color indexed="65"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.000000"/>
-      <color indexed="4"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.000000"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,198 +174,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241899"/>
-        <bgColor theme="9" tint="0.39997558519241899"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810496"/>
-        <bgColor theme="9" tint="0.59999389629810496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241899"/>
-        <bgColor theme="8" tint="0.39997558519241899"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810496"/>
-        <bgColor theme="8" tint="0.59999389629810496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431398"/>
-        <bgColor theme="8" tint="0.79998168889431398"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241899"/>
-        <bgColor theme="7" tint="0.39997558519241899"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810496"/>
-        <bgColor theme="7" tint="0.59999389629810496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810496"/>
-        <bgColor theme="6" tint="0.59999389629810496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241899"/>
-        <bgColor theme="5" tint="0.39997558519241899"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810496"/>
-        <bgColor theme="5" tint="0.59999389629810496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431398"/>
-        <bgColor theme="5" tint="0.79998168889431398"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810496"/>
-        <bgColor theme="4" tint="0.59999389629810496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431398"/>
-        <bgColor theme="4" tint="0.79998168889431398"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241899"/>
-        <bgColor theme="4" tint="0.39997558519241899"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431398"/>
-        <bgColor theme="7" tint="0.79998168889431398"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431398"/>
-        <bgColor theme="6" tint="0.79998168889431398"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="26"/>
-        <bgColor indexed="26"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431398"/>
-        <bgColor theme="9" tint="0.79998168889431398"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241899"/>
-        <bgColor theme="6" tint="0.39997558519241899"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF3CC0DD"/>
         <bgColor indexed="40"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -489,366 +195,61 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="50">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0"/>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="4" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="5" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="6" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="8" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="9" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="10" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="11" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="12" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="13" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="14" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="15" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="16" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="17" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="18" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="19" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="20" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="5" fillId="21" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="22" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="6" fillId="23" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="24" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="7" fillId="0" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="25" borderId="3" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="26" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="27" borderId="4" numFmtId="0" applyNumberFormat="0" applyFont="0" applyFill="1" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="9" fillId="28" borderId="5" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="10" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="11" fillId="25" borderId="5" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="12" fillId="29" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="10" fillId="0" borderId="6" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="14" fillId="0" borderId="7" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="165" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="30" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="15" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="166" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="16" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="17" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="18" fillId="0" borderId="7" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="167" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="19" fillId="31" borderId="8" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="32" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="20" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="21" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="21" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="22" fillId="33" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="22" fillId="33" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="10" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="60% - Accent6" xfId="2" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="3" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="4" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="5" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="6" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="7" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="9" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="10" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="11" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="14" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="15" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="16" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="17" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="18" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="19" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="20" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="21" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="22" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="23" builtinId="32"/>
-    <cellStyle name="Bad" xfId="24" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="25" builtinId="42"/>
-    <cellStyle name="Total" xfId="26" builtinId="25"/>
-    <cellStyle name="Output" xfId="27" builtinId="21"/>
-    <cellStyle name="Currency" xfId="28" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="29" builtinId="38"/>
-    <cellStyle name="Note" xfId="30" builtinId="10"/>
-    <cellStyle name="Input" xfId="31" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="32" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="33" builtinId="22"/>
-    <cellStyle name="Good" xfId="34" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="35" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="36" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="37" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="38" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
-    <cellStyle name="Title" xfId="40" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="41" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="42" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="43" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="44" builtinId="17"/>
-    <cellStyle name="Comma" xfId="45" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="46" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="47" builtinId="40"/>
-    <cellStyle name="Percent" xfId="48" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="49" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1345,25 +746,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="8.78125" defaultRowHeight="14.25"/>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.78125" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.4453125"/>
-    <col customWidth="1" min="2" max="4" width="24.21875"/>
-    <col customWidth="1" min="5" max="5" width="23.109375"/>
-    <col customWidth="1" min="6" max="6" style="1" width="15.890625"/>
-    <col customWidth="1" min="7" max="8" width="28"/>
-    <col customWidth="1" min="9" max="10" width="18.4453125"/>
-    <col customWidth="1" min="11" max="11" width="14.4453125"/>
-    <col customWidth="1" min="12" max="14" width="16.78125"/>
-    <col customWidth="1" min="15" max="15" width="60.78125"/>
+    <col min="1" max="1" width="7.4453125" customWidth="1"/>
+    <col min="2" max="4" width="24.21875" customWidth="1"/>
+    <col min="5" max="5" width="23.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.890625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="11" width="18.4453125" customWidth="1"/>
+    <col min="12" max="12" width="14.4453125" customWidth="1"/>
+    <col min="13" max="15" width="16.78125" customWidth="1"/>
+    <col min="16" max="16" width="60.78125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1" ht="21" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1382,7 +785,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" ht="16.5">
+    <row r="2" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1401,7 +804,7 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
     </row>
-    <row r="3" ht="16.5">
+    <row r="3" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1420,7 +823,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" ht="16.5">
+    <row r="4" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1439,7 +842,7 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" ht="16.5">
+    <row r="5" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1458,7 +861,7 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" ht="16.5">
+    <row r="6" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1475,7 +878,7 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" ht="16.5">
+    <row r="7" ht="16.5" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1491,7 +894,7 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" ht="16.5">
+    <row r="8" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -1512,7 +915,7 @@
       <c r="N8" s="5"/>
       <c r="O8" s="6"/>
     </row>
-    <row r="9" ht="30.899999999999999" customHeight="1">
+    <row r="9" ht="30.9" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
@@ -1558,58 +961,64 @@
       <c r="O9" s="9" t="s">
         <v>20</v>
       </c>
+      <c r="P9" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="10" ht="16.5">
+    <row r="10" ht="16.5" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="12" t="s">
         <v>29</v>
       </c>
+      <c r="I10" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="J10" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="11" t="s">
         <v>31</v>
       </c>
+      <c r="K10" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="L10" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
+    <row r="11" spans="8:16" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="8:16" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/mtb_detected_rr_detected/uk.xlsx
+++ b/api/templates/mtb_detected_rr_detected/uk.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E74DDE-D82F-5F4B-B87F-3A2939B0D770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Виявлено MTB, виявлено RR" state="visible" r:id="rId4"/>
+    <sheet name="Виявлено MTB, виявлено RR" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -133,36 +134,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd-mm-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -188,25 +193,41 @@
       <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -255,291 +276,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -742,31 +480,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.78125" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.4453125" customWidth="1"/>
-    <col min="2" max="4" width="24.21875" customWidth="1"/>
-    <col min="5" max="5" width="23.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.890625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
+    <col min="2" max="4" width="24.1640625" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="11" width="18.4453125" customWidth="1"/>
-    <col min="12" max="12" width="14.4453125" customWidth="1"/>
-    <col min="13" max="15" width="16.78125" customWidth="1"/>
-    <col min="16" max="16" width="60.78125" customWidth="1"/>
+    <col min="10" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="15" width="16.83203125" customWidth="1"/>
+    <col min="16" max="16" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -785,7 +521,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -804,7 +540,7 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
     </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -823,7 +559,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -842,7 +578,7 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -861,7 +597,7 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -878,7 +614,7 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" ht="16.5" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -894,7 +630,7 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -915,7 +651,7 @@
       <c r="N8" s="5"/>
       <c r="O8" s="6"/>
     </row>
-    <row r="9" ht="30.9" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
@@ -965,7 +701,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>22</v>
       </c>
@@ -1015,10 +751,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="8:16" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="8:16" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>